--- a/Result/checksun_type/散裝航運.xlsx
+++ b/Result/checksun_type/散裝航運.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>44.02</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>43.54</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>44.11</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>43.54</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>44.11</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>490057.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>805691.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>805691.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>1303801.7</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>1943788.48</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>1943788.48</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-327585.8476253878</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>490057</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>490057.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>43.92</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>43.49</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>44.13</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>43.49</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>44.13</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>1583750.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>988492.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>988492.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>1433201.6</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>1962099.68</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>1962099.68</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-286606.2440955555</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>1583750</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>1583750.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>43.92</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>43.44</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>44.15</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>43.44</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>44.15</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>662684.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>1002672.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>1002672</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>1878900.6</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>1932234.52</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>1932234.52</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-335009.4089066682</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>662684</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>662684.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>43.95</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>43.4</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>44.17</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>44.17</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>669578.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>1346024.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>1346024.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>2567374.4</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>1964625.26</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>1964625.26</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-293506.522604448</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>669578</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>669578.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>43.98</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>43.37</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>44.21</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>43.37</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>44.21</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>622390.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>1452261.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>1452261.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>2829191.6</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>1985574.38</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>1985574.38</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-224472.9520796891</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>622390</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>622390.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>43.97000000000001</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>43.35</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>44.23</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>43.35</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>44.23</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>1404060.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>1801911.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>1801911.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>3022377.3</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>2002187.04</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>2002187.04</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-112780.8173271874</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>1404060</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>1404060.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>43.98999999999999</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>43.34</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>44.26</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>43.34</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>44.26</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>1654648.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>1877910.8</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>1877910.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>3157131.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>2013435.62</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>2013435.62</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-32943.0956333573</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>1654648</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>1654648.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>43.92</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>43.31</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>44.28</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>43.31</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>44.28</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>2379448.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>2755129.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>2755129.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>3126842.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>2008212.78</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>2008212.78</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>55438.61734473472</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>2379448</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>2379448.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>43.8</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>43.29</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>44.3</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>43.29</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>44.3</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>1200760.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>3788724.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>3788724</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>3111702.4</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>1984167.88</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>1984167.88</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>102061.1138368398</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>1200760</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>1200760.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>43.58</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>43.29</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>44.32</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>43.29</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>44.32</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>2370642.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>4206122.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>4206122</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>3077742.9</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>1975864.68</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>1975864.68</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>291307.6404742454</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>2370642</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>2370642.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>43.28</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>43.29</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>44.35</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>43.29</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>44.35</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1784056.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>4242843.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>4242843</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>3117699.4</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>1949494.58</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>1949494.58</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>425911.4770821738</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1784056</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1784056.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>17.32</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>17.13</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>17.25</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>17.13</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>17.25</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>180414825.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>98326419.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>98326419.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>66165607.0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>54533327.24</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>54533327.24</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>14043149.93220292</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>180414825</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>180414825.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>16.94</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>17.08</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>17.24</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>17.24</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>76796379.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>65517681.2</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>65517681.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>50039637.7</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>52609274.18</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>52609274.18</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>5559029.610550985</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>76796379</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>76796379.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>16.69</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>17.06</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>17.24</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>17.24</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>54764320.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>55195337.8</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>55195337.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>44314449.8</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>51727321.28</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>51727321.28</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>4342297.307814248</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>54764320</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>54764320.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,21 +7077,17 @@
           <t>16.56</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>17.06</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
+      <c r="AM16" t="n">
+        <v>17.06</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="AO16" t="inlineStr">
         <is>
           <t>17.25</t>
         </is>
       </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>17.25</t>
-        </is>
-      </c>
       <c r="AP16" t="inlineStr">
         <is>
           <t>-35.51</t>
@@ -7216,20 +7128,16 @@
           <t>120414635.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>52597917.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>52597917.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>40407484.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>51049122.1</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>51049122.1</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>4809604.007196963</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>120414635</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>120414635.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,21 +7507,17 @@
           <t>16.59</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>17.1</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
+      <c r="AM17" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="AO17" t="inlineStr">
         <is>
           <t>17.26</t>
         </is>
       </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>17.26</t>
-        </is>
-      </c>
       <c r="AP17" t="inlineStr">
         <is>
           <t>-47.47</t>
@@ -7652,20 +7558,16 @@
           <t>59241937.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>41457016.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>41457016.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>30439903.5</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>49017736.72</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>49017736.72</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-1728548.886799045</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>59241937</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>59241937.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>16.63</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>17.14</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>17.27</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>17.14</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>17.27</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>16371135.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>34004794.8</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>34004794.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>26060964.3</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>48223273.52</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>48223273.52</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-4452815.775121946</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>16371135</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>16371135.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>16.78</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>17.19</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>17.29</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>17.29</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>25184662.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>34561594.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>34561594.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>26881265.0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>48257944.14</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>48257944.14</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-3592296.266471736</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>25184662</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>25184662.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,21 +8797,17 @@
           <t>16.91</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
+      <c r="AM20" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="AO20" t="inlineStr">
         <is>
           <t>17.24</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>17.3</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>17.24</t>
-        </is>
-      </c>
       <c r="AP20" t="inlineStr">
         <is>
           <t>-105.97</t>
@@ -8960,20 +8848,16 @@
           <t>41777219.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>33433561.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>33433561.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>27542117.2</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>48101400.24</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>48101400.24</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-3178992.851740308</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>41777219</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>41777219.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>17.02</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>17.3</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>17.32</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>17.32</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>64710131.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>28217051.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>28217051</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>26307966.8</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>47723333.42</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>47723333.42</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-4252797.907418959</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>64710131</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>64710131.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>17.08</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>17.36</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>17.33</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>17.33</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>21980827.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>19422790.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>19422790.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>28294962.6</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>46998831.16</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>46998831.16</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-8092017.204552077</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>21980827</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>21980827.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>17.14</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>17.4</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>17.34</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>17.34</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>19155132.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>18117133.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>18117133.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>39692455.1</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>47709827.04</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>47709827.04</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-8709475.871722527</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>19155132</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>19155132.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>19.94</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>20.48</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>20.93</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>20.93</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>402056.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>145041.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>145041.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>117305.0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>117652.62</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>117652.62</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>19703.36118395778</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>402056</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>402056.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>19.59</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>20.49</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>20.96</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>20.96</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>93109.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>75080.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>75080.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>82826.9</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>121634.48</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>121634.48</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-4750.590122850102</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>93109</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>93109.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>19.45</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>20.53</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>20.98</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>20.98</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>45802.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>68969.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>68969.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>82919.2</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>121978.1</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>121978.1</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-6413.678056759542</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>45802</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>45802.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>19.47</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>20.6</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>21</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>141248.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>78011.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>78011.39999999999</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>84717.2</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>121735.82</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>121735.82</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-3491.850888888759</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>141248</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>141248.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>19.6</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>20.67</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>21.01</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>21.01</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>42994.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>80332.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>80332.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>95420.2</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>119676.24</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>119676.24</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-9419.460260184453</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>42994</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>42994.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>19.67</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>20.75</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>21.03</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>21.03</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>52248.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>89568.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>89568.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>98081.1</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>119669.26</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>119669.26</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-7023.850067028863</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>52248</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>52248.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>19.89</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>20.84</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>21.04</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>20.84</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>21.04</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>62554.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>90573.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>90573.60000000001</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>98248.7</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>119899.08</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>119899.08</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-4342.198002984151</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>62554</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>62554.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>20.06</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>20.91</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>21.06</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>20.91</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>21.06</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>91013.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>96869.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>96869.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>97990.2</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>119683.98</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>119683.98</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-1460.402268527978</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>91013</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>91013.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>20.25</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>21.07</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>21.07</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>152855.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>91423.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>91423</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>94788.9</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>119099.78</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>119099.78</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-340.5725668574451</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>152855</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>152855.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>20.38</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>21.06</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>21.08</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>21.06</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>21.08</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>89171.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>110507.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>110507.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>95813.7</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>117265.54</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>117265.54</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-5354.581115654611</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>89171</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>89171.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>20.72</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>21.14</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>21.09</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>21.09</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>57275.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>106594.0</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>106594</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>114800.1</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>117029.72</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>117029.72</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-5502.929716948609</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>57275</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>57275.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>65.03999999999999</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>63.69</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>62.0</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>63.69</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>62</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>1103203844.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>588167857.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>588167857.6</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>454591478.4</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>354319999.54</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>354319999.54</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>75495819.26453763</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>1103203844</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>1103203844.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>64.16</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>63.48</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>61.83</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>63.48</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>61.83</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>569070826.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>436285555.6</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>436285555.6</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>363206181.6</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>336091951.3</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>336091951.3</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>25072749.99905181</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>569070826</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>569070826.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>63.73999999999999</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>63.35</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>61.71</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>63.35</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>61.71</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>227051913.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>386741890.0</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>386741890</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>321738917.3</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>330070055.38</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>330070055.38</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>9372876.191248715</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>227051913</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>227051913.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>63.58</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>63.25</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>61.6</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>63.25</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>61.6</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>452747380.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>391001329.8</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>391001329.8</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>311857105.6</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>327380985.38</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>327380985.38</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>23254622.99469978</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>452747380</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>452747380.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>63.52</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>63.28</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>61.51</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>63.28</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>61.51</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>588765325.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>404786137.6</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>404786137.6</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>290759229.8</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>320772184.7</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>320772184.7</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>18073510.4283905</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>588765325</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>588765325.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>63.04</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>63.24</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>61.38</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>63.24</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>61.38</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>343792334.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>321015099.2</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>321015099.2</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>259635184.6</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>311948386.28</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>311948386.28</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-4546912.71735096</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>343792334</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>343792334.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>63.02</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>63.26</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>61.29</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>63.26</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>61.29</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>321352498.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>290126807.6</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>290126807.6</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>247845978.7</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>308230552.94</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>308230552.94</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-10452307.0070762</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>321352498</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>321352498.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>62.85999999999999</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>63.26</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>61.17</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>63.26</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>61.17</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>248349112.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>256735944.6</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>256735944.6</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>233687580.5</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>306410311.46</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>306410311.46</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-16111019.74214518</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>248349112</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>248349112.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>62.84</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>63.31</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>61.09</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>63.31</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>61.09</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>521671419.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>232712881.4</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>232712881.4</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>223037282.1</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>304703620.26</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>304703620.26</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-15797710.15859568</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>521671419</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>521671419.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>63.0</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>63.43</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>61.03</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>63.43</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>61.03</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>169910133.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>176732322.0</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>176732322</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>227860266.0</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>298019332.44</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>298019332.44</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-44070453.99786085</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>169910133</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>169910133.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>63.26000000000001</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>63.48</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>60.99</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>63.48</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>60.99</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>189350876.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>198255270.0</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>198255270</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>275911536.9</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>299323607.72</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>299323607.72</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-45197434.05403036</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>189350876</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>189350876.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>29.77</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>29.69</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>28.48</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>29.69</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>28.48</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>112160271.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>45885367.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>45885367.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>33913861.8</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>35914112.28</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>35914112.28</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>4621132.287161537</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>112160271</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>112160271.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>29.33</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>29.58</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>28.4</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>29.58</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>28.4</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>56858860.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>27272307.2</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>27272307.2</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>24605149.5</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>34626506.92</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>34626506.92</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-1743566.540571854</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>56858860</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>56858860.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>29.15</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>29.51</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>28.35</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>29.51</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>28.35</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>8619496.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>19942633.0</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>19942633</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>21333717.7</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>33845778.38</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>33845778.38</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-4848572.02517055</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>8619496</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>8619496.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>29.27</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>29.48</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>28.31</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>29.48</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>28.31</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>37817111.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>21972788.2</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>21972788.2</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>22165387.4</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>33795175.3</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>33795175.3</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-3942627.573698312</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>37817111</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>37817111.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>29.42</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>29.48</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>28.27</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>29.48</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>28.27</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>13971101.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>21055028.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>21055028</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>22120863.5</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>33261963.88</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>33261963.88</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-5635928.979677316</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>13971101</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>13971101.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>29.47</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>29.46</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>28.23</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>28.23</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>19094968.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>21942355.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>21942355.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>27181548.6</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>33181971.58</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>33181971.58</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-5298718.167515986</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>19094968</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>19094968.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>29.71</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>29.48</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>28.2</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>29.48</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>28.2</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>20210489.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>21937991.8</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>21937991.8</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>31267944.0</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>33159141.6</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>33159141.6</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-5176734.251302809</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>20210489</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>20210489.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>29.74</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>29.46</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>28.16</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>28.16</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>18770272.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>22724802.4</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>22724802.4</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>44520941.6</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>32947768.7</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>32947768.7</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-4937108.254880309</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>18770272</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>18770272.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>29.76</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>29.42</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>28.11</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>29.42</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>28.11</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>33228310.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>22357986.6</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>22357986.6</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>44719224.6</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>32805118.0</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>32805118</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-4264151.143745296</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>33228310</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>33228310.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>29.85</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>29.34</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>28.07</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>29.34</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>28.07</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>18407740.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>23186699.0</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>23186699</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>44759036.6</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>32298059.82</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>32298059.82</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-4699568.22984723</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>18407740</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>18407740.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>30.03</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>29.25</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>28.03</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>28.03</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>19073148.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>32420741.4</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>32420741.4</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>53763335.7</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>32393605.02</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>32393605.02</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-3565832.701784015</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>19073148</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>19073148.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>21.99</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>21.16</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>21.32</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>21.32</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>61201616.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>40468172.0</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>40468172</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>39397797.6</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>34077075.82</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>34077075.82</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>4902792.616875194</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>61201616</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>61201616.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>21.76</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>21.09</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>21.3</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>21.09</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>21.3</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>94684873.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>33954777.6</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>33954777.6</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>37209343.9</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>37619491.58</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>37619491.58</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>3752697.85303545</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>94684873</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>94684873.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>21.62</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>21.05</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>21.29</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>21.05</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>21.29</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>19676985.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>21160796.2</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>21160796.2</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>30390773.5</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>38764859.84</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>38764859.84</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-1611811.411486879</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>19676985</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>19676985.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>21.73</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>21.06</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>21.25</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>21.06</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>21.25</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>15077680.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>32890632.4</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>32890632.4</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>31813510.7</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>39241133.84</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>39241133.84</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-1181271.953251384</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>15077680</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>15077680.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>21.79</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>21.1</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>21.23</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>21.23</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>11699706.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>35832568.2</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>35832568.2</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>34076302.1</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>40050562.76</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>40050562.76</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-31244.62172741443</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>11699706</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>11699706.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>21.69</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>21.11</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>21.18</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>21.18</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>28634644.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>38327423.2</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>38327423.2</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>33957246.8</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>40537271.24</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>40537271.24</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>1974693.231225666</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>28634644</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>28634644.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>21.65</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>21.13</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>21.12</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>21.12</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>30714966.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>40463910.2</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>40463910.2</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>32473753.5</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>40235071.06</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>40235071.06</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>2955336.334329158</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>30714966</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>30714966.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>21.49</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>21.1</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>21.06</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>21.06</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>78326166.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>39620750.8</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>39620750.8</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>32053346.7</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>40222369.16</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>40222369.16</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>4027815.683965243</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>78326166</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>78326166.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>21.15</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>21.04</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>21.0</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>21.04</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>21</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>29787359.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>30736389.0</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>30736389</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>25416477.7</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>40736794.5</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>40736794.5</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>314878.4804465994</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>29787359</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>29787359.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>21.0</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>20.99</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>20.94</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>20.94</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>24173981.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>32320036.0</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>32320036</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>24310501.4</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>41306524.98</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>41306524.98</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>200023.2796897329</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>24173981</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>24173981.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>20.72</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>20.97</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>20.88</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>20.88</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>39317079.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>29587070.4</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>29587070.4</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>24521371.2</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>41188254.24</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>41188254.24</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>630234.090048153</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>39317079</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>39317079.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>53.98</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>53.97</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>53.93</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>53.97</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>53.93</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>309731502.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>149304115.8</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>149304115.8</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>110162521.1</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>117855603.56</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>117855603.56</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>16654678.1665608</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>309731502</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>309731502.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>52.7</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>53.86</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>53.88</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>53.86</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>53.88</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>218314058.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>106744330.4</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>106744330.4</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>89222972.2</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>113419591.14</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>113419591.14</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>1495019.715925276</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>218314058</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>218314058.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>51.73999999999999</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>53.87</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>53.87</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>48571438.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>72818195.4</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>72818195.40000001</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>81980229.2</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>111872773.36</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>111872773.36</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-10420302.63197996</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>48571438</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>48571438.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>51.66</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>53.95</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>53.87</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>53.95</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>53.87</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>87014812.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>72647562.4</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>72647562.40000001</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>80519028.5</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>111823206.94</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>111823206.94</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-8883328.749273852</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>87014812</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>87014812.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>51.86</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>54.22</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>53.88</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>54.22</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>53.88</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>82888769.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>74426138.2</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>74426138.2</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>77212396.3</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>110830557.88</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>110830557.88</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-10489322.96150535</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>82888769</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>82888769.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>51.62</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>54.38</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>53.86</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>54.38</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>53.86</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>96932575.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>71020926.4</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>71020926.40000001</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>72937143.1</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>109856642.7</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>109856642.7</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-11966905.69463946</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>96932575</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>96932575.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>51.84</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>54.65</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>53.89</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>53.89</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>48683383.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>71701614.0</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>71701614</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>70664021.5</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>108733892.34</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>108733892.34</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-15155042.18145107</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>48683383</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>48683383.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>52.0</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>54.93</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>53.9</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>54.93</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>53.9</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>47718273.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>91142263.0</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>91142263</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>73006397.7</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>108974522.54</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>108974522.54</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-13998715.08470152</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>47718273</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>47718273.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>52.58</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>55.22</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>53.9</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>55.22</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>53.9</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>95907691.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>88390494.6</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>88390494.59999999</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>76185022.6</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>108723394.98</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>108723394.98</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-11743460.47917713</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>95907691</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>95907691.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>53.06</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>55.56</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>53.91</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>53.91</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>65862710.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>79998654.4</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>79998654.40000001</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>103628419.5</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>108329575.64</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>108329575.64</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-13265410.81131452</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>65862710</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>65862710.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>53.67999999999999</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>55.84</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>53.96</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>55.84</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>53.96</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>100336013.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>74853359.8</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>74853359.8</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>154411688.0</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>108348566.82</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>108348566.82</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-11746755.79253529</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>100336013</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>100336013.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>58.12</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>55.49</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>55.88</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>55.49</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>55.88</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>1494863306.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>691582599.2</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>691582599.2</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>503387043.9</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>334020375.46</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>334020375.46</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>127313601.8441774</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>1494863306</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>1494863306.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>56.48</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>55.09</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>55.74</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>55.09</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>55.74</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>933422961.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>446484163.2</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>446484163.2</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>375839702.7</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>308455166.98</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>308455166.98</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>53599868.699211</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>933422961</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>933422961.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>55.56</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>54.88</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>55.7</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>54.88</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>55.7</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>193243135.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>310940948.0</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>310940948</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>304093628.7</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>297862688.6</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>297862688.6</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>6534577.288572788</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>193243135</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>193243135.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>55.2</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>54.82</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>55.65</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>54.82</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>55.65</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>365882661.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>324774796.4</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>324774796.4</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>294773749.7</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>295959155.16</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>295959155.16</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>18370050.2987836</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>365882661</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>365882661.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>54.96</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>54.89</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>55.63</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>54.89</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>55.63</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>470500933.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>360847901.0</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>360847901</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>267641049.0</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>292076446.16</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>292076446.16</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>16124703.58841383</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>470500933</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>470500933.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>54.32000000000001</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>54.88</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>55.59</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>54.88</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>55.59</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>269371126.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>315191488.6</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>315191488.6</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>231655877.7</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>286214455.96</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>286214455.96</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>1132082.588299394</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>269371126</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>269371126.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>54.24000000000001</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>54.96</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>55.59</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>54.96</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>55.59</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>255706885.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>305195242.2</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>305195242.2</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>217589454.9</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>283087694.18</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>283087694.18</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>1223243.245696664</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>255706885</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>255706885.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>54.04</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>55.04</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>55.6</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>55.04</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>55.6</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>262412377.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>297246309.4</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>297246309.4</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>214724793.1</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>281943022.98</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>281943022.98</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>2773811.318917871</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>262412377</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>262412377.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>54.08000000000001</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>55.11</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>55.62</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>55.11</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>55.62</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>546248184.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>264772703.0</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>264772703</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>209494764.8</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>280318384.7</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>280318384.7</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>4171398.304986775</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>546248184</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>546248184.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>54.2</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>55.28</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>55.65</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>55.28</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>55.65</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>242218871.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>174434197.0</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>174434197</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>196014042.5</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>274934777.32</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>274934777.32</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-24392006.6900928</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>242218871</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>242218871.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>54.34</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>55.41</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>55.7</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>55.41</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>55.7</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>219389894.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>148120266.8</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>148120266.8</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>233212701.4</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>275351747.5</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>275351747.5</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-31751158.62270319</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>219389894</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>219389894.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>24.21</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>23.71</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>23.59</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>23.59</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>533714964.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>213588852.2</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>213588852.2</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>154506617.2</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>130430407.12</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>130430407.12</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>36456643.16839448</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>533714964</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>533714964.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>23.69</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>23.64</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>23.54</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>23.54</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>209346116.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>125353376.0</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>125353376</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>108029248.5</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>121580584.48</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>121580584.48</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>5993187.341536269</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>209346116</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>209346116.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>23.42</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>23.61</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>23.5</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>23.61</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>23.5</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>59645958.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>98376804.0</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>98376804</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>91224351.3</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>119882928.12</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>119882928.12</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>-2986272.530458897</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>59645958</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>59645958.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>23.37</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>23.64</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>23.48</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>23.48</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>142908112.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>100576223.2</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>100576223.2</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>89724797.2</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>119208339.96</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>119208339.96</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>331882.885635823</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>142908112</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>142908112.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>23.48</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>23.73</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>23.46</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>23.73</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>23.46</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>122329111.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>106719336.0</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>106719336</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>80318307.0</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>117089558.7</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>117089558.7</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>-3860693.123001575</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>122329111</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>122329111.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>23.35</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>23.44</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>23.44</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>92537583.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>95424382.2</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>95424382.2</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>71924956.8</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>115109289.06</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>115109289.06</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>-7507312.559519231</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>92537583</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>92537583.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>23.46</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>23.81</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>23.42</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>23.81</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>23.42</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>74463256.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>90705121.0</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>90705121</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>70352707.3</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>113697535.7</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>113697535.7</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>-9256701.16313304</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>74463256</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>74463256.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>23.41</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>23.86</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>23.4</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>23.86</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>23.4</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>70643054.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>84071898.6</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>84071898.59999999</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>71164187.4</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>113000879.68</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>113000879.68</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>-9488696.233898014</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>70643054</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>70643054.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>23.32</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>23.94</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>23.38</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>23.94</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>23.38</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>173623676.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>78873371.2</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>78873371.2</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>69240750.9</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>112256551.34</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>112256551.34</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>-9071928.398065895</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>173623676</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>173623676.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>23.27</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>24.04</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>23.37</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>24.04</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>23.37</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>65854342.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>53917278.0</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>53917278</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>66106473.7</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>109496609.2</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>109496609.2</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>-19186186.40408909</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>65854342</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>65854342.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>23.3</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>24.15</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>23.36</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>23.36</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>68941277.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>48425531.4</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>48425531.4</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>86631108.3</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>109842909.28</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>109842909.28</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>-21403191.11254762</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>68941277</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>68941277.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43443,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43627,11 @@
           <t>5.454000000000001</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>5.62</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>5.73</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>5.73</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43678,16 @@
           <t>9650401.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>6422658.4</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>6422658.4</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>5884071.2</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>6823896.92</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>6823896.92</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43704,10 @@
           <t>115586.6411085632</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>9650401</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>9650401.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43873,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44057,11 @@
           <t>5.436000000000001</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>5.63</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>5.74</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>5.74</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44108,16 @@
           <t>4631800.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>5360029.4</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>5360029.4</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>5523714.8</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>6742493.44</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>6742493.44</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44134,10 @@
           <t>-228892.054090674</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>4631800</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>4631800.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44303,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44487,11 @@
           <t>5.459999999999999</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>5.64</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>5.75</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44538,16 @@
           <t>3779920.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>5631284.2</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>5631284.2</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>5573964.3</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>6733180.76</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>6733180.76</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44564,10 @@
           <t>-175122.5095863463</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>3779920</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>3779920.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44733,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44917,11 @@
           <t>5.504</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>5.67</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>5.76</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>5.76</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44968,16 @@
           <t>9957045.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>6016467.4</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>6016467.4</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>5659241.2</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>6779067.74</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>6779067.74</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44994,10 @@
           <t>-781.6420949371532</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>9957045</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>9957045.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45163,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45347,11 @@
           <t>5.56</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>5.69</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>5.77</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>5.77</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45398,16 @@
           <t>4094126.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>5000620.0</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>5000620</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>5147304.0</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>6683254.94</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>6683254.94</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45424,10 @@
           <t>-413530.1656038184</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>4094126</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>4094126.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45593,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45777,11 @@
           <t>5.588</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>5.7</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>5.78</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>5.78</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45828,16 @@
           <t>4337256.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>5345484.0</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>5345484</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>5284798.2</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>6685705.04</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>6685705.04</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45854,10 @@
           <t>-360232.0861306563</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>4337256</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>4337256.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46023,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46207,11 @@
           <t>5.612</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>5.72</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>5.78</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>5.78</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46258,16 @@
           <t>5988074.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>5687400.2</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>5687400.2</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>5408113.2</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>6681905.74</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>6681905.74</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46284,10 @@
           <t>-297276.1838071868</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>5988074</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>5988074.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46453,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46637,11 @@
           <t>5.638</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>5.73</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>5.79</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>5.79</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46688,16 @@
           <t>5705836.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>5516644.4</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>5516644.4</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>5214011.2</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>6608132.76</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>6608132.76</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46714,10 @@
           <t>-373595.5310662594</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>5705836</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>5705836.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46883,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47067,11 @@
           <t>5.652</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>5.8</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>5.8</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47118,16 @@
           <t>4877808.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>5302015.0</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>5302015</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>5148635.2</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>6558371.44</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>6558371.44</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47144,10 @@
           <t>-439040.6867554253</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>4877808</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>4877808.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47313,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47497,11 @@
           <t>5.664</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>5.77</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>5.8</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>5.8</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47548,16 @@
           <t>5818446.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>5293988.0</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>5293988</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>5338636.9</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>6534634.88</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>6534634.88</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47574,10 @@
           <t>-428136.4560701121</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>5818446</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>5818446.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47743,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47927,11 @@
           <t>5.686</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>5.78</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>5.81</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>5.81</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47978,16 @@
           <t>6046837.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>5224112.4</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>5224112.4</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>6099411.9</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>6493069.06</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>6493069.06</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48004,10 @@
           <t>-498051.0388028743</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>6046837</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>6046837.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
